--- a/Unidad2/pi2/telemetria_servidor.csv.xlsx
+++ b/Unidad2/pi2/telemetria_servidor.csv.xlsx
@@ -8,44 +8,77 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kekky\Documents\duckdb-practica\Unidad2\pi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7AE7E9CF-0E49-409C-B558-CDFF48C2ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5263D8A7-C3BF-41A0-AF1D-24AA07BA63A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{785ADD99-4254-4C1D-894E-601D245F3E7E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{785ADD99-4254-4C1D-894E-601D245F3E7E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gráfico1" sheetId="2" r:id="rId1"/>
-    <sheet name="telemetria_servidor" sheetId="1" r:id="rId2"/>
+    <sheet name="telemetria_servidor" sheetId="1" r:id="rId1"/>
+    <sheet name="cajas_bigotes" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">telemetria_servidor!$B$1</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">telemetria_servidor!$B$2:$B$101</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">telemetria_servidor!$B$1</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">telemetria_servidor!$B$2:$B$101</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">telemetria_servidor!$B$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">telemetria_servidor!$B$2:$B$101</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">telemetria_servidor!$B$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">telemetria_servidor!$B$2:$B$101</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">telemetria_servidor!$B$1</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">telemetria_servidor!$B$2:$B$101</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>peticion_id</t>
   </si>
   <si>
     <t>latencia_ms</t>
   </si>
+  <si>
+    <t>1. Diagrama de Caja y Bigotes</t>
+  </si>
+  <si>
+    <t>2. Conclusiones de ingeniería</t>
+  </si>
+  <si>
+    <t>¿Cuántas peticiones fueron clasificadas como anomalías en total?</t>
+  </si>
+  <si>
+    <t>¿Qué servidor el Rango Intercuartílico (IQR) en el análisis del rendimiento del servidor?</t>
+  </si>
+  <si>
+    <t>¿Qué acciones de infraestructura recomendarías si este servidor estuviera en producción?</t>
+  </si>
+  <si>
+    <t>Se clasificaron 4 de las 100 peticiones como anomalías, es decir, el 4% de la muestra, todas de tipo Spike Alto. Este resultado es consistente con el modelo de simulación: como cada petición tiene 5% de probabilidad de ser anómala, el número esperado es de 5 con una desviación estándar de aproximadamente 2.2, por lo que variaciones entre corridas son normales.</t>
+  </si>
+  <si>
+    <t>El IQR, que en esta ejecución fue de 15.20 ms, representa la amplitud del 50% central de las latencias; es decir, qué tanto varía el tiempo de respuesta durante la operación típica del servidor, sin influencia de los picos. Un IQR pequeño indica un servicio estable y predecible; un IQR grande, un servicio irregular. Además, el IQR define los umbrales de la Regla de Tukey, de modo que el criterio de anomalía se adapta al comportamiento real del servidor en lugar de depender de un valor fijo arbitrario, y no se contamina con los propios picos que busca detectar, a diferencia de un criterio basado en la media y la desviación estándar.</t>
+  </si>
+  <si>
+    <t>1. Monitoreo y alertas: vigilar percentiles altos (p95 y p99) y configurar alertas automáticas cuando la latencia supere el límite de Tukey calculado sobre una ventana móvil, en lugar de basarse solo en el promedio.</t>
+  </si>
+  <si>
+    <t>2. Escalamiento y balanceo de carga: implementar autoescalado horizontal y balanceadores de carga para absorber picos legítimos de tráfico.</t>
+  </si>
+  <si>
+    <t>4. Diagnóstico de memoria: revisar el uso de memoria y el recolector de basura para identificar fugas o bloqueos que expliquen picos aislados.</t>
+  </si>
+  <si>
+    <t>3. Protección contra ataques: aplicar limitación de tasa (rate limiting), un firewall de aplicaciones web y servicios de mitigación de denegación de servicio.</t>
+  </si>
+  <si>
+    <t>5. Tolerancia a fallos: usar caché, timeouts y circuit breakers para evitar que una petición lenta se propague a otros servicios.</t>
+  </si>
+  <si>
+    <t>6. Mejora continua: realizar pruebas de carga periódicas y mantener un procedimiento documentado de respuesta a incidentes, registrando la causa de cada anomalía detectada.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +212,24 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -522,8 +573,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -582,88 +638,12 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -706,7 +686,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-7FF2-4543-9371-6FA1A90A17EF}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>latencia_ms</cx:v>
             </cx:txData>
           </cx:tx>
@@ -788,6 +768,11 @@
       </cx:axis>
     </cx:plotArea>
   </cx:chart>
+  <cx:printSettings>
+    <cx:headerFooter alignWithMargins="1" differentOddEven="0" differentFirst="0"/>
+    <cx:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <cx:pageSetup paperSize="9" firstPageNumber="1" orientation="portrait" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  </cx:printSettings>
 </cx:chartSpace>
 </file>
 
@@ -1324,20 +1309,21 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{0AB9E1BE-4173-4CAF-AAC2-D2EE8606B3CF}">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</chartsheet>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9296400" cy="6070600"/>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
@@ -1345,13 +1331,11 @@
             <xdr:cNvPr id="2" name="Gráfico 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F4C9B21-CD13-2800-820E-CE6C4F9D9EEF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A95B9906-7C85-E76D-C3CB-D656501503C3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
+            <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
             <a:off x="0" y="0"/>
@@ -1365,83 +1349,47 @@
         </xdr:graphicFrame>
       </mc:Choice>
       <mc:Fallback>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="129540" y="476250"/>
+              <a:ext cx="5288280" cy="4796790"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
     <xdr:clientData/>
-  </xdr:absoluteAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
-    <cdr:from>
-      <cdr:x>0</cdr:x>
-      <cdr:y>0</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>1</cdr:x>
-      <cdr:y>1</cdr:y>
-    </cdr:to>
-    <cdr:sp macro="" textlink="">
-      <cdr:nvSpPr>
-        <cdr:cNvPr id="2" name="Rectángulo 1">
-          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE0609A-304E-A075-F3C8-45C86E161823}"/>
-            </a:ext>
-          </a:extLst>
-        </cdr:cNvPr>
-        <cdr:cNvSpPr>
-          <a:spLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noTextEdit="1"/>
-        </cdr:cNvSpPr>
-      </cdr:nvSpPr>
-      <cdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="9296400" cy="6070600"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstClr val="white"/>
-        </a:solidFill>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="1">
-          <a:solidFill>
-            <a:prstClr val="green"/>
-          </a:solidFill>
-        </a:ln>
-      </cdr:spPr>
-      <cdr:txBody>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" horzOverflow="clip"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:r>
-            <a:rPr lang="es-MX" sz="1100"/>
-            <a:t>Este gráfico no está disponible en su versión de Excel.
-Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
-          </a:r>
-        </a:p>
-      </cdr:txBody>
-    </cdr:sp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2576,4 +2524,245 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E01375-F746-4144-8F93-1E4E250B0921}">
+  <dimension ref="A2:G55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="30" spans="1:5" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" ht="4.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A33:G37"/>
+    <mergeCell ref="A40:G47"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>